--- a/XlsxSharp.Tests/Resource/Examples/Columns/ColumnCollection.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Columns/ColumnCollection.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Columns of a Range" sheetId="1" r:id="rId2"/>
-    <x:sheet name="Columns of a worksheet" sheetId="2" r:id="rId3"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Columns of a Range" sheetId="1"/>
+    <sheet r:id="rId2" name="Columns of a worksheet" sheetId="2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -393,113 +393,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:V6"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="22" width="3.710625" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:22">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-    </x:row>
-    <x:row r="2" spans="1:22">
-      <x:c r="A2" s="1"/>
-      <x:c r="B2" s="1"/>
-    </x:row>
-    <x:row r="4" spans="1:22">
-      <x:c r="A4" s="2"/>
-      <x:c r="B4" s="2"/>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4"/>
-      <x:c r="J4" s="5"/>
-      <x:c r="K4" s="5"/>
-      <x:c r="M4" s="5"/>
-      <x:c r="N4" s="5"/>
-      <x:c r="P4" s="6"/>
-      <x:c r="Q4" s="6"/>
-      <x:c r="S4" s="6"/>
-      <x:c r="T4" s="6"/>
-      <x:c r="V4" s="7"/>
-    </x:row>
-    <x:row r="5" spans="1:22">
-      <x:c r="A5" s="2"/>
-      <x:c r="B5" s="2"/>
-      <x:c r="D5" s="3"/>
-      <x:c r="E5" s="3"/>
-      <x:c r="G5" s="4"/>
-      <x:c r="H5" s="4"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-      <x:c r="M5" s="5"/>
-      <x:c r="N5" s="5"/>
-      <x:c r="P5" s="6"/>
-      <x:c r="Q5" s="6"/>
-      <x:c r="S5" s="6"/>
-      <x:c r="T5" s="6"/>
-      <x:c r="V5" s="7"/>
-    </x:row>
-    <x:row r="6" spans="1:22">
-      <x:c r="A6" s="2"/>
-      <x:c r="B6" s="2"/>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-      <x:c r="G6" s="4"/>
-      <x:c r="H6" s="4"/>
-      <x:c r="J6" s="5"/>
-      <x:c r="K6" s="5"/>
-      <x:c r="M6" s="5"/>
-      <x:c r="N6" s="5"/>
-      <x:c r="P6" s="6"/>
-      <x:c r="Q6" s="6"/>
-      <x:c r="S6" s="6"/>
-      <x:c r="T6" s="6"/>
-      <x:c r="V6" s="7"/>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:V6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="22" style="0" customWidth="1" width="3.710625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="V4" s="7"/>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="V5" s="7"/>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="V6" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="2" width="3.710625" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="5" width="3.710625" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="8" width="3.710625" style="4" customWidth="1"/>
-    <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="10" max="11" width="3.710625" style="5" customWidth="1"/>
-    <x:col min="12" max="12" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="13" max="14" width="3.710625" style="5" customWidth="1"/>
-    <x:col min="15" max="15" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="16" max="17" width="3.710625" style="6" customWidth="1"/>
-    <x:col min="18" max="18" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="19" max="20" width="3.710625" style="6" customWidth="1"/>
-    <x:col min="21" max="21" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="3.710625" style="7" customWidth="1"/>
-  </x:cols>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" style="2" customWidth="1" width="3.710625"/>
+    <col min="3" max="3" style="0" customWidth="1" width="3.710625"/>
+    <col min="4" max="5" style="3" customWidth="1" width="3.710625"/>
+    <col min="6" max="6" style="0" customWidth="1" width="3.710625"/>
+    <col min="7" max="8" style="4" customWidth="1" width="3.710625"/>
+    <col min="9" max="9" style="0" customWidth="1" width="3.710625"/>
+    <col min="10" max="11" style="5" customWidth="1" width="3.710625"/>
+    <col min="12" max="12" style="0" customWidth="1" width="3.710625"/>
+    <col min="13" max="14" style="5" customWidth="1" width="3.710625"/>
+    <col min="15" max="15" style="0" customWidth="1" width="3.710625"/>
+    <col min="16" max="17" style="6" customWidth="1" width="3.710625"/>
+    <col min="18" max="18" style="0" customWidth="1" width="3.710625"/>
+    <col min="19" max="20" style="6" customWidth="1" width="3.710625"/>
+    <col min="21" max="21" style="0" customWidth="1" width="3.710625"/>
+    <col min="22" max="22" style="7" customWidth="1" width="3.710625"/>
+  </cols>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>